--- a/mock-data/product-master-data.xlsx
+++ b/mock-data/product-master-data.xlsx
@@ -479,17 +479,17 @@
   <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
@@ -501,7 +501,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PRODUCT MASTER  (variants, status, base UOM, material, grade, configuration)</t>
+          <t>PRODUCT MASTER  (variants, status, base UOM, material, finish, configuration)</t>
         </is>
       </c>
     </row>
@@ -595,17 +595,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-CTG-4520</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Carbon Steel Pipe 4 inch SCH40</t>
+          <t>Ceramic Disc Faucet Cartridge, Single-Control</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>CARTRIDGE</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -615,22 +615,22 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Carbon Steel</t>
+          <t>Ceramic/Brass</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>A106-B</t>
+          <t>Single-Control</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>4 inch</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -653,14 +653,14 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>16</v>
+        <v>0.3</v>
       </c>
       <c r="O3" s="3" t="n">
         <v>7</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>SteelCorp</t>
+          <t>AquaCore</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -672,17 +672,17 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SKU-FLG-3010</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Stainless Steel Flange 3 inch 150#</t>
+          <t>Pop-Up Drain Assembly, Brushed Nickel</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>FLANGE</t>
+          <t>DRAIN</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -697,17 +697,17 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>SS316</t>
+          <t>Solid Brass</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>150#</t>
+          <t>Grid Strainer</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>3 inch</t>
+          <t>1.25 in</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -730,14 +730,14 @@
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>10</v>
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>FlangeTech</t>
+          <t>FlowFit</t>
         </is>
       </c>
       <c r="Q4" s="4" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Ball Valve 2 inch Full Port</t>
+          <t>Pressure-Balancing Shower Valve, 1/2 in</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>SS304</t>
+          <t>Forged Brass</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Class 600</t>
+          <t>Pressure-Balance</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>2 inch</t>
+          <t>1/2 in</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -807,36 +807,36 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>14</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>ValveWorks</t>
+          <t>ThermoGuard</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SKU-PMP-7700</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Centrifugal Pump 5HP</t>
+          <t>Digital Shower Interface System</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>PUMP</t>
+          <t>SHOWERSYS</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Cast Iron</t>
+          <t>Composite/Electronic</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>API-610</t>
+          <t>Smart-Control</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>5HP</t>
+          <t>Wall-Mount</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -884,14 +884,14 @@
         </is>
       </c>
       <c r="N6" s="4" t="n">
-        <v>65</v>
+        <v>6.5</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>28</v>
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>PumpPro</t>
+          <t>AquaSmart</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
@@ -903,17 +903,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SKU-CHM-9100</t>
+          <t>SKU-FIN-9100</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Industrial Solvent Drum</t>
+          <t>Enameled Cast Iron Touch-Up Finish, White</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Solvent</t>
+          <t>Enamel Coating</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Tech-Grade</t>
+          <t>VOC-Grade</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>55 gal</t>
+          <t>1 qt</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -961,14 +961,14 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>200</v>
+        <v>1.2</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>ChemSafe</t>
+          <t>FinishPro</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -980,17 +980,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SKU-CHM-9200</t>
+          <t>SKU-FIN-9200</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Aerosol Degreaser (no SDS on file)</t>
+          <t>Cast Iron Touch-Up Aerosol, Almond (SDS pending)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1005,17 +1005,17 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Solvent</t>
+          <t>Enamel Aerosol</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Tech-Grade</t>
+          <t>VOC-Grade</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>20 gal</t>
+          <t>12 oz</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1038,14 +1038,14 @@
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>80</v>
+        <v>0.5</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>6</v>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>ChemSafe</t>
+          <t>FinishPro</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -1057,17 +1057,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>SKU-GSK-1150</t>
+          <t>SKU-SEL-1150</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Spiral Wound Gasket 3 inch</t>
+          <t>Tank-to-Bowl Gasket Kit</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>GASKET</t>
+          <t>SEAL</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Graphite/SS</t>
+          <t>Rubber/Foam</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Class 150</t>
+          <t>Universal</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>3 inch</t>
+          <t>3 in</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1115,14 +1115,14 @@
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>4</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>SealTech</t>
+          <t>SealRight</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1134,17 +1134,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SKU-OBS-1000</t>
+          <t>SKU-CTG-1000</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Legacy Carbon Pipe 4 inch (obsolete)</t>
+          <t>Legacy 2-Handle Faucet Cartridge (obsolete)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>CARTRIDGE</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1154,22 +1154,22 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Carbon Steel</t>
+          <t>Brass</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>Two-Handle</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>4 inch</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-CTG-4520</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
@@ -1196,14 +1196,14 @@
         </is>
       </c>
       <c r="N10" s="4" t="n">
-        <v>15</v>
+        <v>0.3</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>SteelCorp</t>
+          <t>AquaCore</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
@@ -1215,12 +1215,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>SKU-INA-2000</t>
+          <t>SKU-VLV-2000</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Discontinued Gate Valve 2 inch</t>
+          <t>Discontinued Thermostatic Shower Valve (inactive)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Cast Steel</t>
+          <t>Cast Brass</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Class 300</t>
+          <t>Thermostatic</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2 inch</t>
+          <t>1/2 in</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1277,19 +1277,19 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>ValveWorks</t>
+          <t>ThermoGuard</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1310,9 +1310,9 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1354,17 +1354,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-CTG-4520</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>schedule</t>
+          <t>control_type</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>SCH40</t>
+          <t>Single-Control</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1377,17 +1377,17 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-CTG-4520</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>coating</t>
+          <t>finish</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Polished Chrome</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1400,17 +1400,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SKU-FLG-3010</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>pressure_class</t>
+          <t>finish</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>150#</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1423,17 +1423,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SKU-FLG-3010</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>face_type</t>
+          <t>drain_type</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Raised Face</t>
+          <t>Pop-Up</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Flanged</t>
+          <t>Sweat</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>actuation</t>
+          <t>valve_type</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Pressure-Balance</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1492,7 +1492,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>SKU-PMP-7700</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>460V</t>
+          <t>120V</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1515,17 +1515,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SKU-PMP-7700</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>seal_type</t>
+          <t>control_mode</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Mechanical</t>
+          <t>Touchscreen</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1538,17 +1538,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>SKU-CHM-9100</t>
+          <t>SKU-FIN-9100</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1579,7 +1579,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1619,50 +1619,50 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>CASE</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.28084</v>
+        <v>24</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>CARTRIDGE</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>metres to feet</t>
+          <t>1 case = 24 cartridges</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>CASE</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.3048</v>
+        <v>0.0416667</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>CARTRIDGE</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>feet to metres</t>
+          <t>each to case</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>GASKET</t>
+          <t>SEAL</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1744,7 +1744,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>PALLET</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>FLANGE</t>
+          <t>DRAIN</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>1 pallet = 50 each</t>
+          <t>1 pair = 2 each</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1864,12 +1864,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>SKU-OBS-1000</t>
+          <t>SKU-CTG-1000</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-CTG-4520</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1892,14 +1892,14 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>A106-B supersedes A53; same dimensions</t>
+          <t>Ceramic disc cartridge supersedes legacy two-handle cartridge; same fit</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SKU-INA-2000</t>
+          <t>SKU-VLV-2000</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Ball valve replaces discontinued gate valve</t>
+          <t>Pressure-balancing valve replaces discontinued thermostatic valve</t>
         </is>
       </c>
     </row>
@@ -1948,10 +1948,10 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1986,12 +1986,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>SKU-FLG-3010</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>SKU-GSK-1150</t>
+          <t>SKU-SEL-1150</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3 inch flange pairs with 3 inch gasket</t>
+          <t>Drain assembly pairs with matching seal kit</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>SKU-FLG-3010</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -2023,14 +2023,14 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Flanged valve requires matching flanges</t>
+          <t>Shower valve pairs with digital interface system</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SKU-PMP-7700</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Isolation valve recommended on pump suction</t>
+          <t>Interface requires a compatible pressure-balance valve</t>
         </is>
       </c>
     </row>

--- a/mock-data/product-master-data.xlsx
+++ b/mock-data/product-master-data.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -496,6 +496,9 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -591,6 +594,21 @@
           <t>country_of_origin</t>
         </is>
       </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>pack_size</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>pack_unit</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>requires_compliance_docs</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -668,6 +686,19 @@
           <t>USA</t>
         </is>
       </c>
+      <c r="R3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -745,6 +776,19 @@
           <t>USA</t>
         </is>
       </c>
+      <c r="R4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -822,6 +866,19 @@
           <t>USA</t>
         </is>
       </c>
+      <c r="R5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -899,6 +956,19 @@
           <t>USA</t>
         </is>
       </c>
+      <c r="R6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -976,6 +1046,19 @@
           <t>USA</t>
         </is>
       </c>
+      <c r="R7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>GAL</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1053,6 +1136,19 @@
           <t>USA</t>
         </is>
       </c>
+      <c r="R8" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1130,6 +1226,19 @@
           <t>USA</t>
         </is>
       </c>
+      <c r="R9" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1211,6 +1320,19 @@
           <t>USA</t>
         </is>
       </c>
+      <c r="R10" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1292,10 +1414,23 @@
           <t>USA</t>
         </is>
       </c>
+      <c r="R11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:T1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1572,14 +1707,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1592,25 +1730,40 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>conversion_id</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>from_uom</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>to_uom</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>product_family</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>rounding_rule</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>material_change_threshold_pct</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1619,23 +1772,36 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>UOM-1001</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>CARTRIDGE</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>1 case = 24 cartridges</t>
         </is>
@@ -1644,23 +1810,36 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>UOM-1002</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.0416667</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>CARTRIDGE</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>round_up</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>each to case</t>
         </is>
@@ -1669,23 +1848,36 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>UOM-1003</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>GAL</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.264172</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>FINISH</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>round_half_up</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>litres to US gallons</t>
         </is>
@@ -1694,23 +1886,36 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>UOM-1004</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
           <t>GAL</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="D6" s="4" t="n">
         <v>3.78541</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>FINISH</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>round_half_up</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>US gallons to litres</t>
         </is>
@@ -1719,23 +1924,36 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>UOM-1005</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>SEAL</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>1 box = 12 each</t>
         </is>
@@ -1744,23 +1962,36 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>UOM-1006</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
           <t>PR</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="D8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>DRAIN</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>1 pair = 2 each</t>
         </is>
@@ -1769,23 +2000,36 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>UOM-1007</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
           <t>KG</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>2.20462</v>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>round_half_up</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>kilograms to pounds</t>
         </is>
@@ -1793,7 +2037,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mock-data/product-master-data.xlsx
+++ b/mock-data/product-master-data.xlsx
@@ -1707,7 +1707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1717,13 +1717,13 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>UOM CONVERSIONS  (approved conversion factors)</t>
+          <t>UOM CONVERSIONS  (approved conversion factors — modelled on Sample_data.xlsx uom_conversions)</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>CASE</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1976,11 +1976,11 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>DRAIN</t>
+          <t>SEAL</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>1 pair = 2 each</t>
+          <t>1 case = 12 each (seal kits)</t>
         </is>
       </c>
     </row>
@@ -2005,33 +2005,337 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>DRAIN</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>1 pair = 2 each</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>UOM-1008</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>DRAIN</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>1 case = 6 drain assemblies</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>UOM-1009</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>VALVE</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>1 case = 4 valves</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>UOM-1010</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>PALLET</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>VALVE</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>1 pallet = 48 valves (12 cases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>UOM-1011</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>KG</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>2.20462</v>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>round_half_up</t>
         </is>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G13" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>kilograms to pounds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>UOM-1012</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.453592</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>round_half_up</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>pounds to kilograms</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>UOM-1013</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>DOZ</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>1 dozen = 12 each</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>UOM-1014</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>144</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>1 gross = 144 each</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>UOM-1015</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>FINISH</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>1 case = 12 aerosol cans</t>
         </is>
       </c>
     </row>

--- a/mock-data/product-master-data.xlsx
+++ b/mock-data/product-master-data.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -703,17 +703,17 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SKU-DRN-3010</t>
+          <t>SKU-CTG-4600</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Pop-Up Drain Assembly, Brushed Nickel</t>
+          <t>Ceramic Disc Faucet Cartridge, Dual-Control</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>DRAIN</t>
+          <t>CARTRIDGE</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Solid Brass</t>
+          <t>Ceramic/Brass</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Grid Strainer</t>
+          <t>Dual-Control</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>1.25 in</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="4" t="n">
-        <v>45</v>
+        <v>13.75</v>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
@@ -761,14 +761,14 @@
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>1.1</v>
+        <v>0.32</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>FlowFit</t>
+          <t>AquaCore</t>
         </is>
       </c>
       <c r="Q4" s="4" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="R4" s="4" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="S4" s="4" t="inlineStr">
         <is>
@@ -793,17 +793,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SKU-VLV-2201</t>
+          <t>SKU-CTG-4800</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Pressure-Balancing Shower Valve, 1/2 in</t>
+          <t>Thermostatic Mixing Faucet Cartridge, Single-Control</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>VALVE</t>
+          <t>CARTRIDGE</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -818,17 +818,17 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Forged Brass</t>
+          <t>Ceramic/Brass</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Pressure-Balance</t>
+          <t>Single-Control</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>1/2 in</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="n">
-        <v>88</v>
+        <v>15.9</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>1.4</v>
+        <v>0.35</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="R5" s="3" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
@@ -876,24 +876,24 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SKU-SHS-7700</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Digital Shower Interface System</t>
+          <t>Pop-Up Drain Assembly, Brushed Nickel</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>SHOWERSYS</t>
+          <t>DRAIN</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Composite/Electronic</t>
+          <t>Solid Brass</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Smart-Control</t>
+          <t>Grid Strainer</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Wall-Mount</t>
+          <t>1.25 in</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="n">
-        <v>1450</v>
+        <v>45</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
@@ -941,14 +941,14 @@
         </is>
       </c>
       <c r="N6" s="4" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>AquaSmart</t>
+          <t>FlowFit</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S6" s="4" t="inlineStr">
         <is>
@@ -966,24 +966,24 @@
       </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SKU-FIN-9100</t>
+          <t>SKU-VLV-2201</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Enameled Cast Iron Touch-Up Finish, White</t>
+          <t>Pressure-Balancing Shower Valve, 1/2 in</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FINISH</t>
+          <t>VALVE</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -993,37 +993,37 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>GAL</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Enamel Coating</t>
+          <t>Forged Brass</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>VOC-Grade</t>
+          <t>Pressure-Balance</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>1 qt</t>
+          <t>1/2 in</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
           <t>N</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="n">
-        <v>9.75</v>
+        <v>88</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1031,14 +1031,14 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>FinishPro</t>
+          <t>ThermoGuard</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1047,11 +1047,11 @@
         </is>
       </c>
       <c r="R7" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>GAL</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SKU-FIN-9200</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Cast Iron Touch-Up Aerosol, Almond (SDS pending)</t>
+          <t>Digital Shower Interface System</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>FINISH</t>
+          <t>SHOWERSYS</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1083,37 +1083,37 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>GAL</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Enamel Aerosol</t>
+          <t>Composite/Electronic</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>VOC-Grade</t>
+          <t>Smart-Control</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>12 oz</t>
+          <t>Wall-Mount</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
           <t>N</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4" t="n">
-        <v>14</v>
+        <v>1450</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
@@ -1121,14 +1121,14 @@
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>FinishPro</t>
+          <t>AquaSmart</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="R8" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
@@ -1153,17 +1153,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>SKU-SEL-1150</t>
+          <t>SKU-FIN-9100</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Tank-to-Bowl Gasket Kit</t>
+          <t>Enameled Cast Iron Touch-Up Finish, White</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>SEAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1173,22 +1173,22 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>GAL</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Rubber/Foam</t>
+          <t>Enamel Coating</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Universal</t>
+          <t>VOC-Grade</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>3 in</t>
+          <t>1 qt</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="n">
-        <v>6.25</v>
+        <v>9.75</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1211,14 +1211,14 @@
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>SealRight</t>
+          <t>FinishPro</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1227,202 +1227,562 @@
         </is>
       </c>
       <c r="R9" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>GAL</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SKU-CTG-1000</t>
+          <t>SKU-FIN-9200</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Legacy 2-Handle Faucet Cartridge (obsolete)</t>
+          <t>Cast Iron Touch-Up Aerosol, Almond (SDS pending)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>CARTRIDGE</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>OBSOLETE</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>GAL</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Enamel Aerosol</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>VOC-Grade</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>FinishPro</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Brass</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Two-Handle</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>SKU-CTG-4520</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4" t="inlineStr">
-        <is>
-          <t>AquaCore</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="S10" s="4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>SKU-SEL-1150</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Tank-to-Bowl Gasket Kit</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>SEAL</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Rubber/Foam</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>3 in</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>SealRight</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SKU-CTG-1017</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Kohler Ceramic Disc Pressure-Balance Cartridge (GP-1017285)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Ceramic/Brass</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Pressure-Balance</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>Kohler</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>KIT</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>SKU-DRN-7213</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Kohler Clearflo Cable Bath Drain Kit, Brushed Nickel (K-7213)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>DRAIN</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>KIT</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Solid Brass</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Cable-Operated</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>1.5 in</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>Kohler</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>KIT</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SKU-CTG-1000</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Legacy 2-Handle Faucet Cartridge (obsolete)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>OBSOLETE</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Brass</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Two-Handle</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>SKU-CTG-4520</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>AquaCore</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>SKU-VLV-2000</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Discontinued Thermostatic Shower Valve (inactive)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>VALVE</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>INACTIVE</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Cast Brass</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Thermostatic</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>1/2 in</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>SKU-VLV-2201</t>
         </is>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L15" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N15" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="O11" s="3" t="n">
+      <c r="O15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>ThermoGuard</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
+      <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="S15" s="3" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="T15" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1442,7 +1802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1535,17 +1895,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SKU-DRN-3010</t>
+          <t>SKU-CTG-4600</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>finish</t>
+          <t>control_type</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Brushed Nickel</t>
+          <t>Dual-Control</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1558,22 +1918,22 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SKU-DRN-3010</t>
+          <t>SKU-CTG-4600</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>drain_type</t>
+          <t>finish</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Pop-Up</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -1581,17 +1941,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SKU-VLV-2201</t>
+          <t>SKU-CTG-4800</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>connection_type</t>
+          <t>control_type</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Sweat</t>
+          <t>Single-Control</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1604,17 +1964,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SKU-VLV-2201</t>
+          <t>SKU-CTG-4800</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>valve_type</t>
+          <t>finish</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Pressure-Balance</t>
+          <t>Polished Chrome</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1627,17 +1987,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>SKU-SHS-7700</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>voltage</t>
+          <t>finish</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>120V</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1650,17 +2010,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SKU-SHS-7700</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>control_mode</t>
+          <t>drain_type</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Touchscreen</t>
+          <t>Pop-Up</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1673,25 +2033,117 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>SKU-VLV-2201</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>connection_type</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Sweat</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SKU-VLV-2201</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>valve_type</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Pressure-Balance</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>SKU-SHS-7700</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>voltage</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>120V</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SKU-SHS-7700</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>control_mode</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Touchscreen</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>SKU-FIN-9100</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>color</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1707,7 +2159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1848,164 +2300,164 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>UOM-1003</t>
+          <t>UOM-1020</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>KIT</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>GAL</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.264172</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>FINISH</t>
+          <t>CARTRIDGE</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>round_half_up</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>litres to US gallons</t>
+          <t>1 Kohler service kit = 12 cartridges (EA)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>UOM-1004</t>
+          <t>UOM-1021</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>GAL</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>KIT</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.78541</v>
+        <v>0.25</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>FINISH</t>
+          <t>DRAIN</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>round_half_up</t>
+          <t>round_up</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>US gallons to litres</t>
+          <t>1 Clearflo drain kit = 4 components (drain body, stopper, overflow, cable)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>UOM-1005</t>
+          <t>UOM-1003</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>GAL</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>12</v>
+        <v>0.264172</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>SEAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>round_half_up</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>1 box = 12 each</t>
+          <t>litres to US gallons</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>UOM-1006</t>
+          <t>UOM-1004</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CASE</t>
+          <t>GAL</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>12</v>
+        <v>3.78541</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>SEAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>round_half_up</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>1 case = 12 each (seal kits)</t>
+          <t>US gallons to litres</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>UOM-1007</t>
+          <t>UOM-1005</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2014,11 +2466,11 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>DRAIN</t>
+          <t>SEAL</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -2031,14 +2483,14 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1 pair = 2 each</t>
+          <t>1 box = 12 each</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>UOM-1008</t>
+          <t>UOM-1006</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -2052,11 +2504,11 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>DRAIN</t>
+          <t>SEAL</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -2069,19 +2521,19 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>1 case = 6 drain assemblies</t>
+          <t>1 case = 12 each (seal kits)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>UOM-1009</t>
+          <t>UOM-1007</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>CASE</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2090,11 +2542,11 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>VALVE</t>
+          <t>DRAIN</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -2107,19 +2559,19 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>1 case = 4 valves</t>
+          <t>1 pair = 2 each</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>UOM-1010</t>
+          <t>UOM-1008</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>PALLET</t>
+          <t>CASE</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -2128,11 +2580,11 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>VALVE</t>
+          <t>DRAIN</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -2145,104 +2597,104 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>1 pallet = 48 valves (12 cases)</t>
+          <t>1 case = 6 drain assemblies</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>UOM-1011</t>
+          <t>UOM-1009</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>CASE</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2.20462</v>
+        <v>4</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>VALVE</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>round_half_up</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>kilograms to pounds</t>
+          <t>1 case = 4 valves</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>UOM-1012</t>
+          <t>UOM-1010</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>PALLET</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.453592</v>
+        <v>48</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>VALVE</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>round_half_up</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>pounds to kilograms</t>
+          <t>1 pallet = 48 valves (12 cases)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>UOM-1013</t>
+          <t>UOM-1011</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>DOZ</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>12</v>
+        <v>2.20462</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -2251,36 +2703,36 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>round_half_up</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>1 dozen = 12 each</t>
+          <t>kilograms to pounds</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>UOM-1014</t>
+          <t>UOM-1012</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>144</v>
+        <v>0.453592</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
@@ -2289,27 +2741,27 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>round_half_up</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>1 gross = 144 each</t>
+          <t>pounds to kilograms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>UOM-1015</t>
+          <t>UOM-1013</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CASE</t>
+          <t>DOZ</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2322,7 +2774,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>FINISH</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2334,6 +2786,82 @@
         <v>0</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>1 dozen = 12 each</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>UOM-1014</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>144</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>1 gross = 144 each</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>UOM-1015</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>FINISH</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>1 case = 12 aerosol cans</t>
         </is>
@@ -2353,7 +2881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2447,33 +2975,103 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>SKU-CTG-1000</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>SKU-CTG-4600</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>IN_STOCK</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Dual-control ceramic disc cartridge; same footprint, upgraded ergonomics</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SKU-CTG-1000</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>SKU-CTG-4800</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>FUNCTIONAL</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>IN_STOCK</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Thermostatic mixing cartridge; adds scald protection, needs compatible body</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>SKU-VLV-2000</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>SKU-VLV-2201</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>FUNCTIONAL</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D6" s="4" t="n">
         <v>25.7</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>IN_STOCK</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Pressure-balancing valve replaces discontinued thermostatic valve</t>
         </is>

--- a/mock-data/product-master-data.xlsx
+++ b/mock-data/product-master-data.xlsx
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="R13" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>1 Clearflo drain kit = 4 components (drain body, stopper, overflow, cable)</t>
+          <t>1 Clearflo drain kit = 10 pieces (EA)</t>
         </is>
       </c>
     </row>
